--- a/Result/checksun_type/材料.xlsx
+++ b/Result/checksun_type/材料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>293.9</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>314.2</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>313.06</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>314.2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>313.06</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>215423673.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>178377059.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>178377059.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>203196614.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>342055488.44</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>342055488.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-29757059.1646015</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>215423673</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>215423673.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>291.3</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>315.35</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>312.95</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>315.35</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>312.95</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>145369311.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>201601517.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>201601517</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>213574610.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>341401273.88</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>341401273.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-33232461.61026913</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>145369311</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>145369311.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>291.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>316.75</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>313.05</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>316.75</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>313.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>255529988.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>235452704.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>235452704.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>262643830.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>341945859.18</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>341945859.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-29504624.11799899</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>255529988</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>255529988.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>294.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>318.42</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>313.22</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>318.42</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>313.22</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>148293165.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>208628721.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>208628721.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>273247364.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>345426351.54</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>345426351.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-34928335.08911312</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>148293165</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>148293165.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>298.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>319.8</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>313.4</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>313.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>127269159.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>208479663.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>208479663.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>276125257.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>349062466.22</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>349062466.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-29939393.47323638</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>127269159</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>127269159.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>301.5</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>320.95</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>313.2</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>320.95</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>313.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>331545962.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>228016169.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>228016169.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>310860645.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>348437711.32</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>348437711.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-19490497.8979398</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>331545962</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>331545962.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>306.4</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>322.75</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>313.15</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>313.15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>314625250.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>225547703.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>225547703.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>318140668.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>344419428.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>344419428.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-25754215.32973254</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>314625250</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>314625250.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>310.2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>324.27</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>312.96</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>312.96</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>121410071.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>289834955.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>289834955.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>319654840.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>340158543.92</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>340158543.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-31969656.25623173</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>121410071</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>121410071.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>315.5</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>325.05</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>312.53</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>312.53</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>147547875.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>337866007.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>337866007.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>378484318.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>339527483.9</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>339527483.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-19005457.82065082</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>147547875</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>147547875.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>320.4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>326.12</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>312.18</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>326.12</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>312.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>224951691.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>343770852.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>343770852.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>476802600.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>340098445.2</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>340098445.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2606886.990511954</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>224951691</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>224951691.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>325.1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>326.8</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>311.79</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>326.8</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>311.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>319203632.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>393705122.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>393705122</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>465510492.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>339342581.32</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>339342581.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>12619479.87363327</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>319203632</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>319203632.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>318.8</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>348.48</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>367.45</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>348.48</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>367.45</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>259073884.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>228717376.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>228717376.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>293431512.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>481042889.08</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>481042889.08</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-35024044.91945842</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>259073884</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>259073884.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>314.9</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>350.48</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>368.89</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>350.48</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>368.89</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>86673453.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>261236362.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>261236362.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>300842312.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>491370560.46</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>491370560.46</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-40015166.56547466</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>86673453</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>86673453.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>314.7</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>352.78</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>370.67</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>370.67</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>117241144.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>341116000.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>341116000.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>314298773.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>515382959.98</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>515382959.98</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-27244752.50387371</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>117241144</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>117241144.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>318.8</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>355.1</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>372.73</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>372.73</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>217244184.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>357191856.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>357191856.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>332478318.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>528510477.64</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>528510477.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-11303386.71930546</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>217244184</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>217244184.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>325.4</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>357.45</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>375.03</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>375.03</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>463354216.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>367149929.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>367149929.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>359440217.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>557019768.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>557019768.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1159073.927195787</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>463354216</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>463354216.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>330.9</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>359.5</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>377.22</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>377.22</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>421668815.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>358145648.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>358145648.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>348500702.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>576071545.44</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>576071545.4400001</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-7447738.360916555</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>421668815</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>421668815.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>338.4</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>361.35</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>378.67</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>378.67</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>486071642.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>340448262.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>340448262.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>351528816.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>590762190.96</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>590762190.96</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-15010900.86675858</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>486071642</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>486071642.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>347.5</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>363.5</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>380.48</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>380.48</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>197620426.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>287481546.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>287481546.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>330367833.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>604199364.28</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>604199364.28</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-32179618.0227201</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>197620426</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>197620426.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>353.2</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>364.92</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>381.58</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>364.92</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>381.58</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>267034549.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>307764781.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>307764781.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>336027958.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>623949754.94</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>623949754.9400001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-24651597.3161394</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>267034549</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>267034549.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>357.9</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>366.48</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>382.53</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>382.53</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>418332812.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>351730504.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>351730504.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>363412784.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>652574118.58</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>652574118.58</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-20454095.29544777</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>418332812</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>418332812.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>365.9</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>368.58</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>383.28</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>368.58</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>383.28</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>333181883.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>338855756.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>338855756.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>349472851.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>679806981.48</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>679806981.48</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-29937688.61247945</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>333181883</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>333181883.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>174.8</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>174.25</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>169.68</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>174.25</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>169.68</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>174920.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>330323.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>330323.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>389597.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>211843.7</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>211843.7</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>10191.75853036175</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>174920</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>174920.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>177.5</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>174.42</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>169.77</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>174.42</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>169.77</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>163410.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>540797.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>540797.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>388405.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>210395.5</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>210395.5</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>27168.1896322539</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>163410</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>163410.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>179.6</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>175.02</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>170.11</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>175.02</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>170.11</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>203938.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>573351.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>573351.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>391089.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>209730.88</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>209730.88</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>51683.15586237633</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>203938</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>203938.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>181.2</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>175.6</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>170.27</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>170.27</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>335990.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>559007.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>559007.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>378699.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>207102.88</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>207102.88</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>80516.42348175216</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>335990</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>335990.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>181.6</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>175.75</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>170.28</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>175.75</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>170.28</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>773361.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>525593.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>525593.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>360604.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>201294.06</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>201294.06</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>104682.7906707979</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>773361</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>773361.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>181.2</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>175.1</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>170.06</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>170.06</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1227288.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>448871.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>448871.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>294742.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>186570.02</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>186570.02</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>88606.32270262047</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1227288</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1227288.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>178.8</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>174.2</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>169.75</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>169.75</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>326179.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>236013.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>236013</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>181083.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>163556.08</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>163556.08</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>13840.39265155917</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>326179</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>326179.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>176.4</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>173.75</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>169.66</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>173.75</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>169.66</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>132221.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>208827.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>208827</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>155954.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>158247.22</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>158247.22</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>3085.014269630134</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>132221</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>132221.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>173.4</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>172.7</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>169.57</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>169.57</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>168917.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>198391.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>198391.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>148197.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>158796.84</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>158796.84</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>8391.223214387574</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>168917</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>168917.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>171.8</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>171.9</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>169.65</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>171.9</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>169.65</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>389753.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>195615.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>195615.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>134490.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>162120.26</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>162120.26</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>11740.12087781297</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>389753</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>389753.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>170.5</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>170.55</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>169.86</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>170.55</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>169.86</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>162995.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>140613.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>140613.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>106093.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>175583.3</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>175583.3</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-7556.029634358332</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>162995</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>162995.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>68.24000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>67.42</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>72.65</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>72.65000000000001</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>11691.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>9392.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>9392</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>12244.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>17082.82</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>17082.82</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-515.6961884255525</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>11691</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>11691.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>67.24000000000001</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>67.42</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>72.85</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>72.84999999999999</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>14415.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>9248.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>9248.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>12197.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>17471.6</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>17471.6</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-648.631831957282</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>14415</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>14415.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>66.74</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>67.46</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>73.14</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>73.14</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>5355.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>8027.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>8027.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>12350.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>18120.12</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>18120.12</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-1107.231614432709</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>5355</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>5355.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>67.04</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>67.73</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>73.52</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>73.52</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>8328.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>10449.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>10449.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>12776.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>18950.5</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>18950.5</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-752.1158888821501</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>8328</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>8328.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>68.04</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>68.03</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>73.89</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>73.89</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>7171.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>14004.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>14004.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>12650.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>19648.24</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>19648.24</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-536.482142064131</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>7171</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>7171.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>67.94000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>68.27</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>74.23</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>68.27</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>74.23</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>10973.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>15097.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>15097</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>12981.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>20453.6</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>20453.6</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-85.30957010752718</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>10973</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>10973.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>68.56</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>68.61</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>74.59</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>74.59</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>8309.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>15146.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>15146.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>12888.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>21045.54</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>21045.54</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>154.9123030486044</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>8309</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>8309.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>68.46000000000001</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>68.82</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>74.91</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>68.81999999999999</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>74.91</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>17468.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>16674.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>16674</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>13376.2</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>22215.42</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>22215.42</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>777.9823967341963</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>17468</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>17468.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>67.8</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>68.96</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>75.13</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>75.13</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>26100.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>15103.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>15103.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>12816.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>22464.28</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>22464.28</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>658.9760164016807</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>26100</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>26100.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>66.6</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>75.29</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>75.29000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>12635.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>11297.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>11297.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>12000.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>22575.46</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>22575.46</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-459.4250989448301</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>12635</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>12635.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>66.38</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>69.2</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>75.58</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>75.58</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>11221.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>10866.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>10866.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>12842.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>23276.16</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>23276.16</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-598.0543673346729</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>11221</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>11221.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>1578.0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>1508.25</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>1297.34</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>1508.25</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1297.34</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>8660559640.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>12655765945.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>12655765945.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>9186859988.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>4926093528.12</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>4926093528.12</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>1587065451.454584</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>8660559640</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>8660559640.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>1594.0</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>1506.25</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>1289.84</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>1506.25</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1289.84</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>14268998085.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>11903064950.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>11903064950.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>8830581319.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>4817341249.12</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>4817341249.12</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>2015843897.12149</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>14268998085</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>14268998085.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>1599.0</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>1501.25</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>1281.64</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>1501.25</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1281.64</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>28742044615.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>10298542898.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>10298542898.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>8042654289.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>4598697520.32</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>4598697520.32</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>1955485989.784161</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>28742044615</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>28742044615.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>1612.0</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>1491.75</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>1272.24</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>1491.75</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1272.24</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>6169714440.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>5728226103.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>5728226103</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>5811772650.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>4091228347.42</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>4091228347.42</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>248738065.7385426</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>6169714440</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>6169714440.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>1595.0</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>1478.0</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>1261.84</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>1478</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1261.84</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>5437512946.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>5661854900.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>5661854900.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>5608775910.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>4014085333.32</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>4014085333.32</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>220107190.6469994</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>5437512946</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>5437512946.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>1580.0</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>1460.0</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>1249.74</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1249.74</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>4897054665.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>5717954032.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>5717954032.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>5414291186.7</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>4036813613.2</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>4036813613.2</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>249795129.4931173</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>4897054665</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>4897054665.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>1564.0</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>1445.5</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>1239.34</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>1445.5</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1239.34</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>6246387825.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>5758097688.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>5758097688.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>5400232874.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>4111558830.4</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>4111558830.4</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>341191460.4699583</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>6246387825</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>6246387825.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>1560.0</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>1431.5</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>1227.28</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>1431.5</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1227.28</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>5890460639.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>5786765680.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>5786765680.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>5177128699.2</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>4046244405.4</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>4046244405.4</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>315000828.2772322</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>5890460639</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>5890460639.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>1542.0</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>1415.0</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>1213.96</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>1415</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1213.96</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>5837858428.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>5895319198.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>5895319198.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>5008164336.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>4019510992.36</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>4019510992.36</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>304470665.4920092</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>5837858428</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>5837858428.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>1521.0</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>1203.08</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1203.08</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>5718008605.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>5555696920.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>5555696920</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>4684194498.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>4026606885.46</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>4026606885.46</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>284189574.6384048</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>5718008605</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>5718008605.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>1474.0</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>1379.0</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>1192.48</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>1379</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1192.48</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>5097772945.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>5110628341.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>5110628341</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>4542311051.0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>4058950208.26</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>4058950208.26</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>257908012.5033131</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>5097772945</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>5097772945.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>41.79</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>43.65</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>47.07</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>47.07</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>18788.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>11702.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>11702.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>11910.8</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>21841.68</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>21841.68</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-835.0067717372658</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>18788</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>18788.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>41.26000000000001</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>47.26</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>47.26</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>10470.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>9823.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>9823.799999999999</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>12026.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>22264.28</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>22264.28</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-1547.487138612682</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>10470</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>10470.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>41.17</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>43.97</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>47.52</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>5468.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>11849.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>11849.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>12661.3</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>22603.46</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>22603.46</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-1618.834550627105</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>5468</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>5468.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>41.75</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>44.22</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>12727.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>12695.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>12695.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>17521.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>23333.98</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>23333.98</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-1127.015333839599</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>12727</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>12727.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>42.59</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>44.56</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>48.12</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>48.12</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>11061.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>11822.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>11822.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>17187.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>24177.16</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>24177.16</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-1161.915905077462</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>11061</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>11061.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>43.29</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>44.84</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>48.39</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>48.39</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>9393.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>12118.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>12118.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>17166.1</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>25730.42</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>25730.42</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-991.7768673787868</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>9393</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>9393.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>44.42</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>48.65</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>20598.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>14229.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>14229</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>17330.2</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>25955.2</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>25955.2</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-534.58621111715</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>20598</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>20598.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>45.3</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>45.46</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>48.9</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>9697.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>13473.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>13473.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>17029.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>26019.26</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>26019.26</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-1062.900051774917</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>9697</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>9697.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>45.48</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>45.64</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>49.1</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>8363.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>22347.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>22347.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>17369.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>26332.84</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>26332.84</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-611.7091080083301</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>8363</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>8363.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>45.25</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>45.78</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>49.3</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>12543.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>22552.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>22552.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>18149.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>27319.1</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>27319.1</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>197.6247083728013</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>12543</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>12543.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>45.05</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>49.54</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>49.54</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>19944.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>22213.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>22213.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>18422.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>29048.06</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>29048.06</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>898.9007064753896</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>19944</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>19944.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>56.22000000000001</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>62.87</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>67.83</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>67.83</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>10293.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>11083.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>11083.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>20700.7</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>136791.44</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>136791.44</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-11445.63800460561</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>10293</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>10293.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>56.0</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>63.66</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>67.71</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>67.70999999999999</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>10673.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>11573.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>11573.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>24148.1</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>137247.22</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>137247.22</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-12216.19514664013</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>10673</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>10673.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>55.98</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>67.51</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>67.51000000000001</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>10476.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>14516.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>14516.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>28763.7</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>137144.9</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>137144.9</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-12921.41266573803</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>10476</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>10476.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>56.68000000000001</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>65.72</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>67.35</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>67.34999999999999</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>11205.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>16023.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>16023.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>30735.6</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>137071.78</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>137071.78</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-13446.2800978158</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>11205</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>11205.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>57.58000000000001</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>67.02</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>67.2</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>12769.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>18281.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>18281</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>32346.9</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>136964.9</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>136964.9</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-13793.97356871919</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>12769</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>12769.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>58.22000000000001</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>68.23</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>67.04</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>68.23</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>67.04000000000001</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>12746.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>30318.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>30318.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>33462.5</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>136903.6</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>136903.6</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-13965.6080425555</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>12746</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>12746.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>59.96</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>69.52</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>66.87</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>66.87</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>25386.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>36722.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>36722.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>36467.7</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>136764.72</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>136764.72</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-13709.5641465161</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>25386</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>25386.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>61.16</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>70.59</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>66.7</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>18013.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>43011.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>43011</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>39984.8</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>136338.16</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>136338.16</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-14208.44557551282</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>18013</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>18013.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>62.73999999999999</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>71.51</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>66.48</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>66.48</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>22491.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>45447.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>45447.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>42035.2</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>136121.74</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>136121.74</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-13623.72456066838</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>22491</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>22491.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>64.38000000000001</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>72.4</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>66.26</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>66.26000000000001</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>72955.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>46412.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>46412.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>44962.5</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>135877.48</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>135877.48</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-12781.63294800959</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>72955</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>72955.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>66.44000000000001</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>73.35</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>66.04</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>66.04000000000001</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>44767.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>36606.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>36606.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>49178.3</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>134557.62</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>134557.62</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-16529.01518178241</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>44767</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>44767.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>57.16</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>58.14</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>60.07</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>60.07</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>162030.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>209836.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>209836.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>215755.9</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>550120.9</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>550120.9</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-38160.02218378661</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>162030</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>162030.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>57.23999999999999</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>58.29</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>60.05</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>60.05</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>199284.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>213119.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>213119.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>251269.4</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>555483.94</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>555483.9399999999</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-36671.78477886959</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>199284</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>199284.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>57.36</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>60.09</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>136228.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>212208.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>212208.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>325088.9</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>556448.64</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>556448.64</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-37227.52474402849</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>136228</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>136228.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>57.62</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>273475.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>241628.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>241628.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>353601.2</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>558552.82</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>558552.8199999999</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-29935.8845248259</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>273475</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>58.17999999999999</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>60.16</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>278164.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>235377.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>235377.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>343709.9</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>560862.08</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>560862.08</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-33155.15262150689</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>278164</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>278164.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>58.38000000000001</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>59.01</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>60.14</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>178445.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>221675.6</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>221675.6</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>333361.3</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>566147.36</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>566147.36</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-37072.38730885455</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>178445</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>59.24</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>194731.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>289419.6</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>341561.2</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>568481.84</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-30660.24445832073</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>194731</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>194731.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>59.73999999999999</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>59.51</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>60.1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>283328.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>437969.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>437969.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>356514.8</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>570563.3</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>570563.3</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-22149.96022690379</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>283328</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>283328.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>60.12</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>59.74</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>60.09</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>242218.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>465573.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>465573.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>341803.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>579417.88</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>579417.88</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-18693.87703106157</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>242218</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>242218.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>59.72000000000001</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>59.98</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>60.1</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>209656.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>452042.6</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>452042.6</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>332281.8</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>596784.86</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>596784.86</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-8684.334000177623</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>209656</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>209656.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>59.14</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>60.08</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>60.08</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>517165.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>445047.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>445047</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>339942.5</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>643736.64</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>643736.64</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>9413.953686805733</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>517165</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>517165.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,21 +38897,17 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
+      <c r="AM90" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AO90" t="inlineStr">
         <is>
           <t>39.53</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
       <c r="AP90" t="inlineStr">
         <is>
           <t>-19.58</t>
@@ -39480,20 +38948,16 @@
           <t>201657416.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>252360977.6</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>252360977.6</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>282417854.9</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>423553251.3</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>423553251.3</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-36974729.3629033</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>201657416</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>201657416.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>39.04000000000001</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>39.71</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>40.26</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>40.26</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>195613562.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>255801795.6</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>255801795.6</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>285762642.3</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>457544220.78</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>457544220.78</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-35925485.46414912</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>195613562</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>195613562.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>39.16</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>39.91</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>40.4</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>188357162.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>277240412.8</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>277240412.8</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>297413036.7</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>528814161.92</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>528814161.92</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-32495956.77078068</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>188357162</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>188357162.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>39.25</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>39.94</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>40.53</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>40.53</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>355837208.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>346026858.8</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>346026858.8</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>290442567.6</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>558638708.96</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>558638708.96</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-25658588.75272644</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>355837208</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>355837208.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>39.93</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>40.66</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>40.66</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>320339540.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>322944767.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>322944767</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>273188557.9</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>613979125.7</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>613979125.7</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-32918832.62862295</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>320339540</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>320339540.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>40.74</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>218861506.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>312474732.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>312474732.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>262014209.7</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>631667121.94</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>631667121.9400001</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-38311615.42888141</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>218861506</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>218861506.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>39.55</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>39.83</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>40.77</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>40.77</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>302806648.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>315723489.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>315723489</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>267936291.1</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>654424013.3</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>654424013.3</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-33774672.37821913</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>302806648</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>302806648.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>39.57000000000001</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>40.87</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>40.87</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>532289392.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>317585660.6</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>317585660.6</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>263274442.8</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>673739372.28</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>673739372.28</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-35081209.22090816</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>532289392</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>532289392.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>39.51000000000001</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>39.76</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>41</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>240426749.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>234858276.4</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>234858276.4</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>236240878.5</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>679732391.62</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>679732391.62</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-60282226.95257431</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>240426749</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>240426749.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>39.5</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>41.14</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>267989366.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>223432348.8</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>223432348.8</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>270578244.9</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>693037521.34</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>693037521.34</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-62859746.71379119</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>267989366</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>267989366.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>39.52</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>39.72</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>41.21</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>41.21</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>235105290.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>211553687.2</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>211553687.2</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>317718579.4</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>694915339.42</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>694915339.42</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-67250064.3828941</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>235105290</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>235105290.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>17.68</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>19.05</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>19.05</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>27545944.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>32561534.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>32561534.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>51519003.4</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>82205412.14</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>82205412.14</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-5110856.075542763</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>27545944</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>27545944.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>17.62</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>19.1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>41265824.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>34157774.2</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>34157774.2</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>52942274.3</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>97003735.86</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>97003735.86</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-4541392.253075995</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>41265824</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>41265824.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>17.62</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>18.49</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>19.18</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>19.18</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>24630282.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>36415219.6</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>36415219.6</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>51242747.6</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>125077625.38</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>125077625.38</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-5035667.069085032</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>24630282</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>24630282.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>17.85</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>18.61</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>19.23</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>19.23</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>41343469.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>45429471.0</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>45429471</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>51469072.0</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>135512407.44</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>135512407.44</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-3779549.196630619</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>41343469</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>41343469.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>18.24</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>19.26</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>28022154.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>60780539.6</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>60780539.6</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>49039304.3</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>137304471.88</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>137304471.88</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-3640809.800387502</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>28022154</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>28022154.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>18.52</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>18.78</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>19.28</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>35527142.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>70476472.2</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>70476472.2</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>48367971.6</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>140530781.3</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>140530781.3</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-1885297.991454914</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>35527142</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>35527142.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>18.76</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>19.29</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>52553051.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>71726774.4</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>71726774.40000001</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>47912479.7</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>140353737.84</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>140353737.84</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-114197.7647135556</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>52553051</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>52553051.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>19.29</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>69701539.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>66070275.6</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>66070275.6</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>46567948.0</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>139781443.8</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>139781443.8</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>595819.372228153</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>69701539</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>69701539.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>19.28</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>118098812.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>57508673.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>57508673</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>42493200.7</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>139366944.98</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>139366944.98</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-248487.6954346895</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>118098812</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>118098812.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>18.75</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>18.94</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>19.26</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>76501817.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>37298069.0</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>37298069</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>33598142.9</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>138751251.62</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>138751251.62</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-6631188.195830375</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>76501817</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>76501817.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>18.65</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>18.94</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>19.25</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>41778653.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>26259471.0</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>26259471</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>33359343.4</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>138380212.08</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>138380212.08</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-11055682.72511597</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>41778653</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>41778653.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
